--- a/backend/sekolah/templates/template_siswa_tabel_D4DA6B98FCFD71C58F5A_20232.xlsx
+++ b/backend/sekolah/templates/template_siswa_tabel_D4DA6B98FCFD71C58F5A_20232.xlsx
@@ -14,201 +14,54 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
-  <si>
-    <t>Nama</t>
-  </si>
-  <si>
-    <t>NIPD</t>
-  </si>
-  <si>
-    <t>JK</t>
-  </si>
-  <si>
-    <t>NISN</t>
-  </si>
-  <si>
-    <t>Tempat Lahir</t>
-  </si>
-  <si>
-    <t>Tanggal Lahir</t>
-  </si>
-  <si>
-    <t>NIK</t>
-  </si>
-  <si>
-    <t>Agama</t>
-  </si>
-  <si>
-    <t>Alamat</t>
-  </si>
-  <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>RW</t>
-  </si>
-  <si>
-    <t>Dusun</t>
-  </si>
-  <si>
-    <t>Kelurahan</t>
-  </si>
-  <si>
-    <t>Kecamatan</t>
-  </si>
-  <si>
-    <t>Kode Pos</t>
-  </si>
-  <si>
-    <t>Jenis Tinggal</t>
-  </si>
-  <si>
-    <t>Alat Transportasi</t>
-  </si>
-  <si>
-    <t>Telepon</t>
-  </si>
-  <si>
-    <t>HP</t>
-  </si>
-  <si>
-    <t>E-Mail</t>
-  </si>
-  <si>
-    <t>SKHUN</t>
-  </si>
-  <si>
-    <t>Penerima KPS</t>
-  </si>
-  <si>
-    <t>No. KPS</t>
-  </si>
-  <si>
-    <t>Nama Ayah</t>
-  </si>
-  <si>
-    <t>Tahun Lahir Ayah</t>
-  </si>
-  <si>
-    <t>Jenjang Pendidikan Ayah</t>
-  </si>
-  <si>
-    <t>Pekerjaan Ayah</t>
-  </si>
-  <si>
-    <t>Penghasilan Ayah</t>
-  </si>
-  <si>
-    <t>NIK Ayah</t>
-  </si>
-  <si>
-    <t>Nama Ibu</t>
-  </si>
-  <si>
-    <t>Tahun Lahir Ibu</t>
-  </si>
-  <si>
-    <t>Jenjang Pendidikan Ibu</t>
-  </si>
-  <si>
-    <t>Pekerjaan Ibu</t>
-  </si>
-  <si>
-    <t>Penghasilan Ibu</t>
-  </si>
-  <si>
-    <t>NIK Ibu</t>
-  </si>
-  <si>
-    <t>Nama Wali</t>
-  </si>
-  <si>
-    <t>Tahun Lahir Wali</t>
-  </si>
-  <si>
-    <t>Jenjang Pendidikan Wali</t>
-  </si>
-  <si>
-    <t>Pekerjaan Wali</t>
-  </si>
-  <si>
-    <t>Penghasilan Wali</t>
-  </si>
-  <si>
-    <t>NIK Wali</t>
-  </si>
-  <si>
-    <t>Rombel Saat Ini</t>
-  </si>
-  <si>
-    <t>No Peserta Ujian Nasional</t>
-  </si>
-  <si>
-    <t>No Seri Ijazah</t>
-  </si>
-  <si>
-    <t>Penerima KIP</t>
-  </si>
-  <si>
-    <t>Nomor KIP</t>
-  </si>
-  <si>
-    <t>Nama di KIP</t>
-  </si>
-  <si>
-    <t>Nomor KKS</t>
-  </si>
-  <si>
-    <t>No Registrasi Akta Lahir</t>
-  </si>
-  <si>
-    <t>Bank</t>
-  </si>
-  <si>
-    <t>Nomor Rekening Bank</t>
-  </si>
-  <si>
-    <t>Rekening Atas Nama</t>
-  </si>
-  <si>
-    <t>Layak PIP (usulan dari sekolah)</t>
-  </si>
-  <si>
-    <t>Alasan Layak PIP</t>
-  </si>
-  <si>
-    <t>Kebutuhan Khusus</t>
-  </si>
-  <si>
-    <t>Sekolah Asal</t>
-  </si>
-  <si>
-    <t>Anak ke-berapa</t>
-  </si>
-  <si>
-    <t>Lintang</t>
-  </si>
-  <si>
-    <t>Bujur</t>
-  </si>
-  <si>
-    <t>No KK</t>
-  </si>
-  <si>
-    <t>Berat Badan</t>
-  </si>
-  <si>
-    <t>Tinggi Badan</t>
-  </si>
-  <si>
-    <t>Lingkar Kepala</t>
-  </si>
-  <si>
-    <t>Jml. Saudara Kandung</t>
-  </si>
-  <si>
-    <t>Jarak Rumah ke Sekolah (KM)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+  <si>
+    <t>nis</t>
+  </si>
+  <si>
+    <t>nisn</t>
+  </si>
+  <si>
+    <t>nm_siswa</t>
+  </si>
+  <si>
+    <t>tempat_lahir</t>
+  </si>
+  <si>
+    <t>tanggal_lahir</t>
+  </si>
+  <si>
+    <t>jenis_kelamin</t>
+  </si>
+  <si>
+    <t>agama</t>
+  </si>
+  <si>
+    <t>alamat_siswa</t>
+  </si>
+  <si>
+    <t>telepon_siswa</t>
+  </si>
+  <si>
+    <t>diterima_tanggal</t>
+  </si>
+  <si>
+    <t>nm_ayah</t>
+  </si>
+  <si>
+    <t>nm_ibu</t>
+  </si>
+  <si>
+    <t>pekerjaan_ayah</t>
+  </si>
+  <si>
+    <t>pekerjaan_ibu</t>
+  </si>
+  <si>
+    <t>nm_wali</t>
+  </si>
+  <si>
+    <t>pekerjaan_wali</t>
   </si>
 </sst>
 </file>
@@ -564,153 +417,6 @@
       <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AK1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AL1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BB1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BD1" t="s">
-        <v>55</v>
-      </c>
-      <c r="BE1" t="s">
-        <v>56</v>
-      </c>
-      <c r="BF1" t="s">
-        <v>57</v>
-      </c>
-      <c r="BG1" t="s">
-        <v>58</v>
-      </c>
-      <c r="BH1" t="s">
-        <v>59</v>
-      </c>
-      <c r="BI1" t="s">
-        <v>60</v>
-      </c>
-      <c r="BJ1" t="s">
-        <v>61</v>
-      </c>
-      <c r="BK1" t="s">
-        <v>62</v>
-      </c>
-      <c r="BL1" t="s">
-        <v>63</v>
-      </c>
-      <c r="BM1" t="s">
-        <v>64</v>
-      </c>
     </row>
   </sheetData>
 </worksheet>
